--- a/naver_코스피200_result.xlsx
+++ b/naver_코스피200_result.xlsx
@@ -469,32 +469,32 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>183,550</t>
+          <t>180,100</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>하락5,450</t>
+          <t>하락8,900</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-2.88%</t>
+          <t>-4.71%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>9,183,807</t>
+          <t>32,036,851</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1,693,737</t>
+          <t>5,834,939</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>10,865,495</t>
+          <t>10,661,268</t>
         </is>
       </c>
     </row>
@@ -509,32 +509,32 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>958,000</t>
+          <t>933,000</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>하락37,000</t>
+          <t>하락62,000</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-3.72%</t>
+          <t>-6.23%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1,205,065</t>
+          <t>4,637,355</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1,160,326</t>
+          <t>4,391,534</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6,827,689</t>
+          <t>6,649,513</t>
         </is>
       </c>
     </row>
@@ -549,32 +549,32 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>494,500</t>
+          <t>490,000</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>하락6,500</t>
+          <t>하락11,000</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-1.30%</t>
+          <t>-2.20%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>237,014</t>
+          <t>954,312</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>117,328</t>
+          <t>469,080</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1,012,527</t>
+          <t>1,003,313</t>
         </is>
       </c>
     </row>
@@ -589,32 +589,32 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>386,500</t>
+          <t>384,500</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>하락7,500</t>
+          <t>하락9,500</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-1.90%</t>
+          <t>-2.41%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>64,723</t>
+          <t>274,036</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>25,248</t>
+          <t>105,845</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>904,410</t>
+          <t>899,730</t>
         </is>
       </c>
     </row>
@@ -629,32 +629,32 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>574,000</t>
+          <t>558,000</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>하락31,000</t>
+          <t>하락47,000</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-5.12%</t>
+          <t>-7.77%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>156,251</t>
+          <t>600,617</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>90,813</t>
+          <t>342,127</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>758,180</t>
+          <t>737,046</t>
         </is>
       </c>
     </row>
@@ -669,32 +669,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1,595,000</t>
+          <t>1,585,000</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>상승10,000</t>
+          <t>보합0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>+0.63%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>7,202</t>
+          <t>30,266</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>11,537</t>
+          <t>48,241</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>738,341</t>
+          <t>733,712</t>
         </is>
       </c>
     </row>
@@ -709,32 +709,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1,407,000</t>
+          <t>1,369,000</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>상승7,000</t>
+          <t>하락31,000</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>+0.50%</t>
+          <t>-2.21%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>47,026</t>
+          <t>158,093</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>66,230</t>
+          <t>219,679</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>725,497</t>
+          <t>705,903</t>
         </is>
       </c>
     </row>
@@ -749,32 +749,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>102,200</t>
+          <t>100,900</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>하락400</t>
+          <t>하락1,700</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-0.39%</t>
+          <t>-1.66%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>694,821</t>
+          <t>2,606,562</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>71,260</t>
+          <t>264,427</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>654,653</t>
+          <t>646,326</t>
         </is>
       </c>
     </row>
@@ -789,32 +789,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>156,600</t>
+          <t>154,700</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>하락1,300</t>
+          <t>하락3,200</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-0.82%</t>
+          <t>-2.03%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>235,395</t>
+          <t>836,058</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>36,681</t>
+          <t>129,985</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>611,387</t>
+          <t>603,969</t>
         </is>
       </c>
     </row>
@@ -829,32 +829,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>151,900</t>
+          <t>152,200</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>상승2,500</t>
+          <t>상승2,800</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>+1.67%</t>
+          <t>+1.87%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>271,438</t>
+          <t>1,058,520</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>41,053</t>
+          <t>160,852</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>566,360</t>
+          <t>567,478</t>
         </is>
       </c>
     </row>
@@ -869,32 +869,32 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>524,000</t>
+          <t>511,000</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>상승1,000</t>
+          <t>하락12,000</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>-2.29%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>49,576</t>
+          <t>179,100</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>25,919</t>
+          <t>92,595</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>549,997</t>
+          <t>536,352</t>
         </is>
       </c>
     </row>
@@ -909,32 +909,32 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>285,500</t>
+          <t>278,000</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>하락3,500</t>
+          <t>하락11,000</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-1.21%</t>
+          <t>-3.81%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>81,272</t>
+          <t>357,312</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>23,379</t>
+          <t>100,125</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>485,283</t>
+          <t>472,535</t>
         </is>
       </c>
     </row>
@@ -949,32 +949,32 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>205,000</t>
+          <t>203,000</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>상승1,500</t>
+          <t>하락500</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>+0.74%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>122,043</t>
+          <t>441,074</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>25,087</t>
+          <t>89,929</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>473,649</t>
+          <t>469,028</t>
         </is>
       </c>
     </row>
@@ -989,32 +989,32 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>225,000</t>
+          <t>222,000</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>하락2,500</t>
+          <t>하락5,500</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>-1.10%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>44,612</t>
+          <t>381,148</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>10,096</t>
+          <t>85,525</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>450,000</t>
+          <t>444,000</t>
         </is>
       </c>
     </row>
@@ -1029,32 +1029,32 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>93,500</t>
+          <t>93,400</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>상승1,400</t>
+          <t>상승1,300</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>+1.52%</t>
+          <t>+1.41%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>208,806</t>
+          <t>1,065,634</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>19,471</t>
+          <t>99,684</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>443,802</t>
+          <t>443,327</t>
         </is>
       </c>
     </row>
@@ -1069,32 +1069,32 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>128,400</t>
+          <t>125,700</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>상승3,700</t>
+          <t>상승1,000</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>+2.97%</t>
+          <t>+0.80%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>398,864</t>
+          <t>932,262</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>51,274</t>
+          <t>118,594</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>393,435</t>
+          <t>385,162</t>
         </is>
       </c>
     </row>
@@ -1109,32 +1109,32 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>67,800</t>
+          <t>65,300</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>상승500</t>
+          <t>하락2,000</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>+0.74%</t>
+          <t>-2.97%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1,605,563</t>
+          <t>3,636,252</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>108,821</t>
+          <t>243,863</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>376,505</t>
+          <t>362,622</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>47,798</t>
+          <t>198,820</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>19,024</t>
+          <t>79,160</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1189,32 +1189,32 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>982,000</t>
+          <t>965,000</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>하락10,000</t>
+          <t>하락27,000</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>-1.01%</t>
+          <t>-2.72%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>25,128</t>
+          <t>82,589</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>24,873</t>
+          <t>80,704</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>353,983</t>
+          <t>347,855</t>
         </is>
       </c>
     </row>
@@ -1229,32 +1229,32 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>457,500</t>
+          <t>457,000</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>상승3,000</t>
+          <t>상승2,500</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>+0.66%</t>
+          <t>+0.55%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>182,439</t>
+          <t>486,526</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>83,754</t>
+          <t>222,335</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>341,724</t>
+          <t>341,350</t>
         </is>
       </c>
     </row>
@@ -1269,32 +1269,32 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>216,000</t>
+          <t>211,500</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>상승500</t>
+          <t>하락4,000</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>-1.86%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>92,733</t>
+          <t>414,759</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20,023</t>
+          <t>88,578</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>338,802</t>
+          <t>331,743</t>
         </is>
       </c>
     </row>
@@ -1304,37 +1304,37 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>고려아연</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>406,000</t>
+          <t>1,546,000</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>상승2,000</t>
+          <t>하락47,000</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>+0.50%</t>
+          <t>-2.95%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>147,452</t>
+          <t>16,077</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>60,097</t>
+          <t>24,912</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>327,177</t>
+          <t>322,696</t>
         </is>
       </c>
     </row>
@@ -1344,37 +1344,37 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>고려아연</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1,569,000</t>
+          <t>396,500</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>하락24,000</t>
+          <t>하락7,500</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>-1.86%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>3,457</t>
+          <t>455,849</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>5,437</t>
+          <t>183,218</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>327,497</t>
+          <t>319,522</t>
         </is>
       </c>
     </row>
@@ -1389,32 +1389,32 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>109,000</t>
+          <t>108,800</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>상승300</t>
+          <t>상승100</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>168,093</t>
+          <t>781,449</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>18,338</t>
+          <t>85,336</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>303,375</t>
+          <t>302,818</t>
         </is>
       </c>
     </row>
@@ -1429,32 +1429,32 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>46,200</t>
+          <t>46,000</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>하락250</t>
+          <t>하락450</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-0.97%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>446,561</t>
+          <t>1,498,854</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20,575</t>
+          <t>69,021</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>296,587</t>
+          <t>295,303</t>
         </is>
       </c>
     </row>
@@ -1469,32 +1469,32 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>347,000</t>
+          <t>342,500</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>상승5,000</t>
+          <t>상승500</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>+1.46%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>93,051</t>
+          <t>258,671</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>32,350</t>
+          <t>89,275</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>280,837</t>
+          <t>277,195</t>
         </is>
       </c>
     </row>
@@ -1504,37 +1504,37 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>효성중공업</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>294,000</t>
+          <t>2,860,000</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>하락6,000</t>
+          <t>하락130,000</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-2.00%</t>
+          <t>-4.35%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>134,940</t>
+          <t>43,757</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>39,665</t>
+          <t>127,499</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>280,218</t>
+          <t>266,682</t>
         </is>
       </c>
     </row>
@@ -1544,37 +1544,37 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>효성중공업</t>
+          <t>HD한국조선해양</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2,916,000</t>
+          <t>375,000</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>하락74,000</t>
+          <t>하락10,000</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>-2.47%</t>
+          <t>-2.60%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>13,784</t>
+          <t>171,510</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>41,113</t>
+          <t>65,114</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>271,904</t>
+          <t>265,399</t>
         </is>
       </c>
     </row>
@@ -1584,37 +1584,37 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>HD한국조선해양</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>382,500</t>
+          <t>278,000</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>하락2,500</t>
+          <t>하락22,000</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>-0.65%</t>
+          <t>-7.33%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>49,318</t>
+          <t>650,100</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>18,981</t>
+          <t>186,453</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>270,707</t>
+          <t>264,968</t>
         </is>
       </c>
     </row>
@@ -1624,37 +1624,37 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>LS ELECTRIC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>135,800</t>
+          <t>834,000</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>하락800</t>
+          <t>하락10,000</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>-0.59%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>345,050</t>
+          <t>94,565</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>46,637</t>
+          <t>79,627</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>256,553</t>
+          <t>250,200</t>
         </is>
       </c>
     </row>
@@ -1664,37 +1664,37 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LS ELECTRIC</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>849,000</t>
+          <t>129,700</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>상승5,000</t>
+          <t>하락6,900</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-5.05%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>22,866</t>
+          <t>872,669</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>19,453</t>
+          <t>116,209</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>254,700</t>
+          <t>245,028</t>
         </is>
       </c>
     </row>
@@ -1709,32 +1709,32 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>349,000</t>
+          <t>336,500</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>상승3,000</t>
+          <t>하락9,500</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>+0.87%</t>
+          <t>-2.75%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>34,194</t>
+          <t>175,762</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>11,902</t>
+          <t>60,287</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>253,034</t>
+          <t>243,972</t>
         </is>
       </c>
     </row>
@@ -1749,32 +1749,32 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>33,000</t>
+          <t>33,200</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>보합0</t>
+          <t>상승200</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>+0.61%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>198,169</t>
+          <t>1,582,887</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>6,543</t>
+          <t>52,639</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>242,245</t>
+          <t>243,713</t>
         </is>
       </c>
     </row>
@@ -1789,32 +1789,32 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>27,000</t>
+          <t>26,350</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>상승150</t>
+          <t>하락500</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>+0.56%</t>
+          <t>-1.86%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>944,248</t>
+          <t>2,633,712</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>25,660</t>
+          <t>70,581</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>237,600</t>
+          <t>231,880</t>
         </is>
       </c>
     </row>
@@ -1829,32 +1829,32 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>320,000</t>
+          <t>314,000</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>상승2,000</t>
+          <t>하락4,000</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>+0.63%</t>
+          <t>-1.26%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>50,622</t>
+          <t>213,144</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>16,236</t>
+          <t>67,583</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>225,895</t>
+          <t>221,660</t>
         </is>
       </c>
     </row>
@@ -1869,32 +1869,32 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>49,350</t>
+          <t>48,650</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>상승300</t>
+          <t>하락400</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>+0.61%</t>
+          <t>-0.82%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>272,215</t>
+          <t>1,231,106</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>13,417</t>
+          <t>60,295</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>218,505</t>
+          <t>215,406</t>
         </is>
       </c>
     </row>
@@ -1909,32 +1909,32 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>271,500</t>
+          <t>266,500</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>상승6,500</t>
+          <t>상승1,500</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>+2.45%</t>
+          <t>+0.57%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>28,743</t>
+          <t>118,098</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>7,727</t>
+          <t>31,736</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>214,466</t>
+          <t>210,517</t>
         </is>
       </c>
     </row>
@@ -1949,32 +1949,32 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>460,000</t>
+          <t>453,000</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>하락30,000</t>
+          <t>하락37,000</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>-6.12%</t>
+          <t>-7.55%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>31,739</t>
+          <t>123,567</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>14,820</t>
+          <t>56,664</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>211,651</t>
+          <t>208,431</t>
         </is>
       </c>
     </row>
@@ -1989,32 +1989,32 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>191,900</t>
+          <t>189,800</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>상승1,200</t>
+          <t>하락900</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>+0.63%</t>
+          <t>-0.47%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>219,834</t>
+          <t>644,522</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>42,074</t>
+          <t>123,436</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>209,444</t>
+          <t>207,152</t>
         </is>
       </c>
     </row>
@@ -2029,32 +2029,32 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1,246,000</t>
+          <t>1,239,000</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>하락4,000</t>
+          <t>하락11,000</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>-0.88%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>13,818</t>
+          <t>50,777</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>17,246</t>
+          <t>63,101</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>201,775</t>
+          <t>200,642</t>
         </is>
       </c>
     </row>
@@ -2069,32 +2069,32 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>114,700</t>
+          <t>114,200</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>상승3,300</t>
+          <t>상승2,800</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>+2.96%</t>
+          <t>+2.51%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>64,479</t>
+          <t>339,679</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>7,359</t>
+          <t>39,169</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>193,844</t>
+          <t>192,999</t>
         </is>
       </c>
     </row>
@@ -2109,32 +2109,32 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>111,900</t>
+          <t>111,300</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>하락2,200</t>
+          <t>하락2,800</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>-1.93%</t>
+          <t>-2.45%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>68,818</t>
+          <t>300,798</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>7,741</t>
+          <t>33,711</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>189,170</t>
+          <t>188,156</t>
         </is>
       </c>
     </row>
@@ -2144,37 +2144,37 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>기업은행</t>
+          <t>HMM</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>23,500</t>
+          <t>19,810</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>상승100</t>
+          <t>하락120</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>-0.60%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>148,945</t>
+          <t>2,230,264</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>3,495</t>
+          <t>44,355</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>187,395</t>
+          <t>186,855</t>
         </is>
       </c>
     </row>
@@ -2184,37 +2184,37 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>HMM</t>
+          <t>기업은행</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>19,840</t>
+          <t>23,400</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>하락90</t>
+          <t>보합0</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>-0.45%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>433,879</t>
+          <t>1,247,215</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>8,655</t>
+          <t>29,306</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>187,138</t>
+          <t>186,598</t>
         </is>
       </c>
     </row>
@@ -2229,32 +2229,32 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>114,200</t>
+          <t>113,000</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>하락500</t>
+          <t>하락1,700</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>-1.48%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>114,461</t>
+          <t>580,909</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>13,064</t>
+          <t>65,612</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>186,016</t>
+          <t>184,062</t>
         </is>
       </c>
     </row>
@@ -2264,37 +2264,37 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>포스코퓨처엠</t>
+          <t>한국항공우주</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>207,750</t>
+          <t>188,000</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>상승5,250</t>
+          <t>상승3,000</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>+2.59%</t>
+          <t>+1.62%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>109,967</t>
+          <t>701,333</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>22,799</t>
+          <t>131,848</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>184,786</t>
+          <t>183,253</t>
         </is>
       </c>
     </row>
@@ -2304,37 +2304,37 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>한국항공우주</t>
+          <t>KT&amp;G</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>188,300</t>
+          <t>155,500</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>상승3,300</t>
+          <t>하락400</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>+1.78%</t>
+          <t>-0.26%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>255,821</t>
+          <t>217,390</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>48,044</t>
+          <t>34,106</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>183,546</t>
+          <t>178,322</t>
         </is>
       </c>
     </row>
@@ -2344,37 +2344,37 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>KT&amp;G</t>
+          <t>포스코퓨처엠</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>156,500</t>
+          <t>200,000</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>상승600</t>
+          <t>하락2,500</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>+0.38%</t>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>38,350</t>
+          <t>286,831</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>6,030</t>
+          <t>58,615</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>179,469</t>
+          <t>177,892</t>
         </is>
       </c>
     </row>
@@ -2389,32 +2389,32 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>80,600</t>
+          <t>80,000</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>상승800</t>
+          <t>상승200</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>+1.00%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>199,052</t>
+          <t>830,279</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>16,057</t>
+          <t>67,026</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>173,121</t>
+          <t>171,832</t>
         </is>
       </c>
     </row>
@@ -2424,37 +2424,37 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>현대건설</t>
+          <t>현대글로비스</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>154,800</t>
+          <t>227,500</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>하락3,100</t>
+          <t>하락2,000</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>-1.96%</t>
+          <t>-0.87%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>229,881</t>
+          <t>91,329</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>35,788</t>
+          <t>20,809</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>172,379</t>
+          <t>170,625</t>
         </is>
       </c>
     </row>
@@ -2464,37 +2464,37 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>현대글로비스</t>
+          <t>현대건설</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>230,000</t>
+          <t>152,400</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>상승500</t>
+          <t>하락5,500</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>-3.48%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>20,484</t>
+          <t>664,482</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>4,698</t>
+          <t>102,305</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>172,500</t>
+          <t>169,706</t>
         </is>
       </c>
     </row>
@@ -2509,32 +2509,32 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>747,000</t>
+          <t>735,000</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>상승13,000</t>
+          <t>상승1,000</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>+1.77%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>163,145</t>
+          <t>415,383</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>122,124</t>
+          <t>309,979</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>164,340</t>
+          <t>161,700</t>
         </is>
       </c>
     </row>
@@ -2549,32 +2549,32 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>60,600</t>
+          <t>59,700</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>상승500</t>
+          <t>하락400</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>+0.83%</t>
+          <t>-0.67%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>60,432</t>
+          <t>284,675</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>3,655</t>
+          <t>17,222</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>152,725</t>
+          <t>150,457</t>
         </is>
       </c>
     </row>
@@ -2584,37 +2584,37 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>포스코인터내셔널</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>88,700</t>
+          <t>78,200</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>하락100</t>
+          <t>상승2,400</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>+3.17%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>63,989</t>
+          <t>1,053,948</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>5,639</t>
+          <t>81,551</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>136,795</t>
+          <t>137,572</t>
         </is>
       </c>
     </row>
@@ -2624,37 +2624,37 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>하이브</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>314,000</t>
+          <t>87,500</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>상승9,500</t>
+          <t>하락1,300</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>+3.12%</t>
+          <t>-1.46%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>110,442</t>
+          <t>205,366</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>33,837</t>
+          <t>18,075</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>135,233</t>
+          <t>134,944</t>
         </is>
       </c>
     </row>
@@ -2669,32 +2669,32 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>542,000</t>
+          <t>533,000</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>상승2,000</t>
+          <t>하락7,000</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>+0.37%</t>
+          <t>-1.30%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>14,031</t>
+          <t>49,618</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>7,698</t>
+          <t>26,681</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>134,866</t>
+          <t>132,627</t>
         </is>
       </c>
     </row>
@@ -2704,37 +2704,37 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>포스코인터내셔널</t>
+          <t>하이브</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>75,000</t>
+          <t>304,000</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>하락800</t>
+          <t>하락500</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>-1.06%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>99,700</t>
+          <t>379,373</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>7,505</t>
+          <t>116,151</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>131,942</t>
+          <t>130,926</t>
         </is>
       </c>
     </row>
@@ -2749,32 +2749,32 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>112,000</t>
+          <t>112,300</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>하락1,300</t>
+          <t>하락1,000</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>-1.15%</t>
+          <t>-0.88%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>63,392</t>
+          <t>299,511</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>7,132</t>
+          <t>33,804</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>126,093</t>
+          <t>126,430</t>
         </is>
       </c>
     </row>
@@ -2789,32 +2789,32 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>180,100</t>
+          <t>175,900</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>하락14,600</t>
+          <t>하락18,800</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>-7.50%</t>
+          <t>-9.66%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61,297</t>
+          <t>387,700</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>11,202</t>
+          <t>69,023</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>124,961</t>
+          <t>122,046</t>
         </is>
       </c>
     </row>
@@ -2824,37 +2824,37 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>에이피알</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>329,000</t>
+          <t>156,100</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>상승500</t>
+          <t>하락3,400</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>-2.13%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>80,303</t>
+          <t>136,693</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>26,361</t>
+          <t>21,491</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>123,172</t>
+          <t>120,787</t>
         </is>
       </c>
     </row>
@@ -2864,37 +2864,37 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>한국금융지주</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>159,100</t>
+          <t>216,000</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>하락400</t>
+          <t>하락4,500</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>-2.04%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>16,551</t>
+          <t>189,257</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2,633</t>
+          <t>41,017</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>123,108</t>
+          <t>120,368</t>
         </is>
       </c>
     </row>
@@ -2904,37 +2904,37 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>한국금융지주</t>
+          <t>NH투자증권</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>220,000</t>
+          <t>33,250</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>하락500</t>
+          <t>하락1,050</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>-3.06%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>41,903</t>
+          <t>750,858</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>9,147</t>
+          <t>25,240</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>122,597</t>
+          <t>118,484</t>
         </is>
       </c>
     </row>
@@ -2944,37 +2944,37 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NH투자증권</t>
+          <t>카카오뱅크</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>34,000</t>
+          <t>24,500</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>하락300</t>
+          <t>하락50</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>-0.87%</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>159,683</t>
+          <t>582,098</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>5,427</t>
+          <t>14,244</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>121,157</t>
+          <t>116,876</t>
         </is>
       </c>
     </row>
@@ -2984,37 +2984,37 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>카카오뱅크</t>
+          <t>에이피알</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>24,650</t>
+          <t>310,000</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>상승100</t>
+          <t>하락18,500</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>-5.63%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>118,479</t>
+          <t>406,921</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2,900</t>
+          <t>129,276</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>117,591</t>
+          <t>116,058</t>
         </is>
       </c>
     </row>
@@ -3029,32 +3029,32 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>245,000</t>
+          <t>241,500</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>상승4,500</t>
+          <t>상승1,000</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>+1.87%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>29,604</t>
+          <t>127,397</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>7,229</t>
+          <t>31,197</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>116,145</t>
+          <t>114,486</t>
         </is>
       </c>
     </row>
@@ -3069,32 +3069,32 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>431,500</t>
+          <t>418,500</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>하락500</t>
+          <t>하락13,500</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-3.12%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>17,881</t>
+          <t>62,038</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>7,646</t>
+          <t>26,224</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>113,103</t>
+          <t>109,696</t>
         </is>
       </c>
     </row>
@@ -3109,32 +3109,32 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>399,000</t>
+          <t>387,500</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>하락6,500</t>
+          <t>하락18,000</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>-1.60%</t>
+          <t>-4.44%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>17,993</t>
+          <t>60,473</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>7,181</t>
+          <t>23,825</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>109,422</t>
+          <t>106,268</t>
         </is>
       </c>
     </row>
@@ -3149,32 +3149,32 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>25,150</t>
+          <t>24,950</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>하락250</t>
+          <t>하락450</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>-0.98%</t>
+          <t>-1.77%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>285,980</t>
+          <t>1,190,173</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>7,180</t>
+          <t>29,838</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>92,607</t>
+          <t>91,871</t>
         </is>
       </c>
     </row>
@@ -3189,32 +3189,32 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>1,222,000</t>
+          <t>1,188,000</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>상승6,000</t>
+          <t>하락28,000</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>-2.30%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>9,125</t>
+          <t>36,089</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>11,160</t>
+          <t>43,554</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>92,053</t>
+          <t>89,492</t>
         </is>
       </c>
     </row>
@@ -3224,37 +3224,37 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>한화</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>120,700</t>
+          <t>277,000</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>상승4,000</t>
+          <t>하락6,500</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>+3.43%</t>
+          <t>-2.29%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>57,699</t>
+          <t>147,333</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>6,863</t>
+          <t>41,524</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>90,475</t>
+          <t>86,424</t>
         </is>
       </c>
     </row>
@@ -3264,37 +3264,37 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>이수페타시스</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>286,000</t>
+          <t>115,000</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>상승2,500</t>
+          <t>하락5,300</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>+0.88%</t>
+          <t>-4.41%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>36,858</t>
+          <t>700,012</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>10,559</t>
+          <t>82,114</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>89,232</t>
+          <t>84,421</t>
         </is>
       </c>
     </row>
@@ -3309,32 +3309,32 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>97,700</t>
+          <t>94,500</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>하락100</t>
+          <t>하락3,300</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-3.37%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>46,704</t>
+          <t>283,903</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>4,540</t>
+          <t>27,210</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>87,246</t>
+          <t>84,388</t>
         </is>
       </c>
     </row>
@@ -3344,37 +3344,37 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>이수페타시스</t>
+          <t>한화</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>118,500</t>
+          <t>111,100</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>하락1,800</t>
+          <t>하락5,600</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>-1.50%</t>
+          <t>-4.80%</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>265,631</t>
+          <t>379,203</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>31,458</t>
+          <t>43,477</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>86,990</t>
+          <t>83,279</t>
         </is>
       </c>
     </row>
@@ -3384,37 +3384,37 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>한진칼</t>
+          <t>HD현대마린솔루션</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>123,500</t>
+          <t>178,900</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>하락3,200</t>
+          <t>하락2,500</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>-2.53%</t>
+          <t>-1.38%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>24,254</t>
+          <t>61,367</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2,992</t>
+          <t>11,014</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>82,451</t>
+          <t>80,203</t>
         </is>
       </c>
     </row>
@@ -3429,32 +3429,32 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>138,400</t>
+          <t>136,000</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>상승1,600</t>
+          <t>하락800</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>+1.17%</t>
+          <t>-0.58%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>24,904</t>
+          <t>122,626</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>3,418</t>
+          <t>16,828</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>80,954</t>
+          <t>79,550</t>
         </is>
       </c>
     </row>
@@ -3464,37 +3464,37 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>HD현대마린솔루션</t>
+          <t>한진칼</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>179,700</t>
+          <t>118,300</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>하락1,700</t>
+          <t>하락8,400</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>-0.94%</t>
+          <t>-6.63%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>11,923</t>
+          <t>107,159</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2,157</t>
+          <t>12,938</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>80,562</t>
+          <t>78,980</t>
         </is>
       </c>
     </row>
@@ -3509,32 +3509,32 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>100,200</t>
+          <t>99,000</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>상승1,300</t>
+          <t>상승100</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>+1.31%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>71,100</t>
+          <t>194,867</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>7,142</t>
+          <t>19,448</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>79,807</t>
+          <t>78,851</t>
         </is>
       </c>
     </row>
@@ -3544,37 +3544,37 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>44,650</t>
+          <t>94,700</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>하락350</t>
+          <t>하락2,500</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>-0.78%</t>
+          <t>-2.57%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>832,959</t>
+          <t>214,470</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>37,810</t>
+          <t>20,550</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>76,750</t>
+          <t>74,163</t>
         </is>
       </c>
     </row>
@@ -3584,37 +3584,37 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>LG이노텍</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>96,800</t>
+          <t>303,000</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>하락400</t>
+          <t>하락10,000</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-3.19%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>50,802</t>
+          <t>204,500</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>4,962</t>
+          <t>63,326</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>75,807</t>
+          <t>71,711</t>
         </is>
       </c>
     </row>
@@ -3624,37 +3624,37 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>LG이노텍</t>
+          <t>한국타이어앤테크놀로지</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>311,500</t>
+          <t>57,400</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>하락1,500</t>
+          <t>하락700</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>73,561</t>
+          <t>306,690</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>23,184</t>
+          <t>17,655</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>73,723</t>
+          <t>71,104</t>
         </is>
       </c>
     </row>
@@ -3664,37 +3664,37 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>한미약품</t>
+          <t>카카오페이</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>567,000</t>
+          <t>52,500</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>상승26,000</t>
+          <t>하락1,500</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>+4.81%</t>
+          <t>-2.78%</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>26,724</t>
+          <t>399,753</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>14,716</t>
+          <t>21,144</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>72,638</t>
+          <t>70,993</t>
         </is>
       </c>
     </row>
@@ -3704,37 +3704,37 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>카카오페이</t>
+          <t>한미약품</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>53,600</t>
+          <t>551,000</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>하락400</t>
+          <t>상승10,000</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>-0.74%</t>
+          <t>+1.85%</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>110,205</t>
+          <t>104,774</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>5,907</t>
+          <t>58,430</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>72,480</t>
+          <t>70,589</t>
         </is>
       </c>
     </row>
@@ -3744,37 +3744,37 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>한국타이어앤테크놀로지</t>
+          <t>LG유플러스</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>57,800</t>
+          <t>15,950</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>하락300</t>
+          <t>상승350</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>-0.52%</t>
+          <t>+2.24%</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>55,731</t>
+          <t>955,437</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>3,229</t>
+          <t>15,248</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>71,600</t>
+          <t>68,558</t>
         </is>
       </c>
     </row>
@@ -3784,37 +3784,37 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>LG유플러스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>15,920</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>상승320</t>
+          <t>하락510</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>+2.05%</t>
+          <t>-3.11%</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>146,884</t>
+          <t>18,195,757</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2,315</t>
+          <t>292,545</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>68,429</t>
+          <t>66,084</t>
         </is>
       </c>
     </row>
@@ -3824,37 +3824,37 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>16,250</t>
+          <t>32,900</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>하락160</t>
+          <t>하락800</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>-0.98%</t>
+          <t>-2.37%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>7,022,548</t>
+          <t>2,474,239</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>112,573</t>
+          <t>82,143</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>67,539</t>
+          <t>64,484</t>
         </is>
       </c>
     </row>
@@ -3864,37 +3864,37 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>32,625</t>
+          <t>36,800</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>하락1,075</t>
+          <t>하락8,200</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>-3.19%</t>
+          <t>-18.22%</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>676,001</t>
+          <t>10,597,245</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>22,278</t>
+          <t>409,911</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>63,945</t>
+          <t>63,256</t>
         </is>
       </c>
     </row>
@@ -3904,37 +3904,37 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>삼성카드</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>68,800</t>
+          <t>54,500</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>하락1,400</t>
+          <t>하락1,900</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>-1.99%</t>
+          <t>-3.37%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>36,553</t>
+          <t>129,972</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2,532</t>
+          <t>7,115</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>63,926</t>
+          <t>63,143</t>
         </is>
       </c>
     </row>
@@ -3944,37 +3944,37 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>삼성카드</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>54,800</t>
+          <t>67,800</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>하락1,600</t>
+          <t>하락2,400</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>-2.84%</t>
+          <t>-3.42%</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>33,201</t>
+          <t>215,310</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>1,838</t>
+          <t>14,756</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>63,491</t>
+          <t>62,997</t>
         </is>
       </c>
     </row>
@@ -3989,32 +3989,32 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>166,000</t>
+          <t>163,900</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>하락2,800</t>
+          <t>하락4,900</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>-1.66%</t>
+          <t>-2.90%</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>38,047</t>
+          <t>145,464</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>6,342</t>
+          <t>23,983</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>63,445</t>
+          <t>62,643</t>
         </is>
       </c>
     </row>
@@ -4024,37 +4024,37 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CJ</t>
+          <t>LG씨엔에스</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>210,500</t>
+          <t>61,200</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>상승500</t>
+          <t>하락1,300</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>-2.08%</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>13,792</t>
+          <t>370,512</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2,897</t>
+          <t>22,884</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>61,418</t>
+          <t>59,294</t>
         </is>
       </c>
     </row>
@@ -4064,37 +4064,37 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>LG씨엔에스</t>
+          <t>CJ</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>62,000</t>
+          <t>203,000</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>하락500</t>
+          <t>하락7,000</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>-3.33%</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>103,524</t>
+          <t>67,308</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>6,443</t>
+          <t>13,922</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>60,069</t>
+          <t>59,229</t>
         </is>
       </c>
     </row>
@@ -4104,37 +4104,37 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>두산밥캣</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>61,700</t>
+          <t>144,500</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>보합0</t>
+          <t>하락800</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-0.55%</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>49,050</t>
+          <t>1,039,855</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>3,020</t>
+          <t>150,927</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>59,143</t>
+          <t>58,265</t>
         </is>
       </c>
     </row>
@@ -4144,37 +4144,37 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>두산밥캣</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>146,100</t>
+          <t>60,500</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>상승800</t>
+          <t>하락1,200</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>+0.55%</t>
+          <t>-1.94%</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>377,459</t>
+          <t>232,821</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>54,550</t>
+          <t>14,221</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>58,910</t>
+          <t>57,993</t>
         </is>
       </c>
     </row>
@@ -4189,32 +4189,32 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>11,710</t>
+          <t>11,530</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>하락40</t>
+          <t>하락220</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>-0.34%</t>
+          <t>-1.87%</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>684,960</t>
+          <t>2,781,164</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>8,002</t>
+          <t>32,401</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>58,550</t>
+          <t>57,650</t>
         </is>
       </c>
     </row>
@@ -4229,32 +4229,32 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>18,650</t>
+          <t>18,430</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>상승200</t>
+          <t>하락20</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>+1.08%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>97,088</t>
+          <t>567,429</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>1,801</t>
+          <t>10,518</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>57,876</t>
+          <t>57,193</t>
         </is>
       </c>
     </row>
@@ -4269,32 +4269,32 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>30,250</t>
+          <t>30,000</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>상승600</t>
+          <t>상승350</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>+2.02%</t>
+          <t>+1.18%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>53,821</t>
+          <t>281,164</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>1,607</t>
+          <t>8,469</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>56,947</t>
+          <t>56,476</t>
         </is>
       </c>
     </row>
@@ -4309,32 +4309,32 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>87,100</t>
+          <t>85,400</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>하락1,700</t>
+          <t>하락3,400</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>-1.91%</t>
+          <t>-3.83%</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>30,874</t>
+          <t>128,695</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2,698</t>
+          <t>11,112</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>56,458</t>
+          <t>55,356</t>
         </is>
       </c>
     </row>
@@ -4349,32 +4349,32 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>29,800</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>하락500</t>
+          <t>하락1,300</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>-1.65%</t>
+          <t>-4.29%</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>625,567</t>
+          <t>1,768,774</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>18,930</t>
+          <t>52,432</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>55,561</t>
+          <t>54,070</t>
         </is>
       </c>
     </row>
@@ -4384,37 +4384,37 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>산일전기</t>
+          <t>오리온</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>173,800</t>
+          <t>132,200</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>상승8,000</t>
+          <t>하락1,900</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>+4.83%</t>
+          <t>-1.42%</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>329,237</t>
+          <t>137,116</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>57,656</t>
+          <t>18,187</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>53,088</t>
+          <t>52,267</t>
         </is>
       </c>
     </row>
@@ -4424,37 +4424,37 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>오리온</t>
+          <t>코웨이</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>133,600</t>
+          <t>73,300</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>하락500</t>
+          <t>하락800</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>-0.37%</t>
+          <t>-1.08%</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>21,163</t>
+          <t>173,624</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2,813</t>
+          <t>12,751</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>52,820</t>
+          <t>51,873</t>
         </is>
       </c>
     </row>
@@ -4464,37 +4464,37 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>코웨이</t>
+          <t>산일전기</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>73,500</t>
+          <t>168,600</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>하락600</t>
+          <t>상승2,800</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>-0.81%</t>
+          <t>+1.69%</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>37,327</t>
+          <t>578,365</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2,748</t>
+          <t>100,051</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>52,014</t>
+          <t>51,499</t>
         </is>
       </c>
     </row>
@@ -4509,32 +4509,32 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>71,700</t>
+          <t>69,900</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>상승1,300</t>
+          <t>하락500</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>+1.85%</t>
+          <t>-0.71%</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>638,440</t>
+          <t>1,910,504</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>45,428</t>
+          <t>136,348</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>50,591</t>
+          <t>49,321</t>
         </is>
       </c>
     </row>
@@ -4549,32 +4549,32 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>225,000</t>
+          <t>225,500</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>하락2,500</t>
+          <t>하락2,000</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>-1.10%</t>
+          <t>-0.88%</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>23,697</t>
+          <t>94,990</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>5,400</t>
+          <t>21,496</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>48,474</t>
+          <t>48,582</t>
         </is>
       </c>
     </row>
@@ -4584,37 +4584,37 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>포스코DX</t>
+          <t>KCC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>31,400</t>
+          <t>525,000</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>하락100</t>
+          <t>하락8,000</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>-1.50%</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>50,852</t>
+          <t>20,538</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>1,601</t>
+          <t>10,716</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>47,739</t>
+          <t>46,654</t>
         </is>
       </c>
     </row>
@@ -4629,32 +4629,32 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>35,600</t>
+          <t>34,950</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>하락100</t>
+          <t>하락750</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>-2.10%</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>113,887</t>
+          <t>520,560</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>4,043</t>
+          <t>18,398</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>47,507</t>
+          <t>46,639</t>
         </is>
       </c>
     </row>
@@ -4664,37 +4664,37 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>KCC</t>
+          <t>포스코DX</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>524,000</t>
+          <t>30,350</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>하락9,000</t>
+          <t>하락1,150</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>-1.69%</t>
+          <t>-3.65%</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2,788</t>
+          <t>337,809</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>1,465</t>
+          <t>10,379</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>46,565</t>
+          <t>46,143</t>
         </is>
       </c>
     </row>
@@ -4704,37 +4704,37 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>넷마블</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>51,800</t>
+          <t>51,500</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>상승3,050</t>
+          <t>상승100</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>+6.26%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>556,923</t>
+          <t>178,988</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>28,949</t>
+          <t>9,303</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>43,226</t>
+          <t>42,210</t>
         </is>
       </c>
     </row>
@@ -4744,37 +4744,37 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>넷마블</t>
+          <t>한화생명</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>52,100</t>
+          <t>4,730</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>상승700</t>
+          <t>하락240</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>+1.36%</t>
+          <t>-4.83%</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>54,768</t>
+          <t>5,475,520</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2,872</t>
+          <t>26,438</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>42,701</t>
+          <t>41,081</t>
         </is>
       </c>
     </row>
@@ -4784,37 +4784,37 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>한화생명</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>4,870</t>
+          <t>49,200</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>하락100</t>
+          <t>상승450</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>-2.01%</t>
+          <t>+0.92%</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>1,810,605</t>
+          <t>954,574</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>8,850</t>
+          <t>48,752</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>42,297</t>
+          <t>41,056</t>
         </is>
       </c>
     </row>
@@ -4829,32 +4829,32 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>3,955</t>
+          <t>3,895</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>하락100</t>
+          <t>하락160</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>-2.47%</t>
+          <t>-3.95%</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2,110,396</t>
+          <t>5,311,346</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>8,375</t>
+          <t>20,896</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>40,589</t>
+          <t>39,973</t>
         </is>
       </c>
     </row>
@@ -4869,32 +4869,32 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>18,130</t>
+          <t>18,240</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>하락10</t>
+          <t>상승100</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.55%</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>100,677</t>
+          <t>743,013</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>1,826</t>
+          <t>13,556</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>38,787</t>
+          <t>39,023</t>
         </is>
       </c>
     </row>
@@ -4909,32 +4909,32 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>100,900</t>
+          <t>98,100</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>하락1,200</t>
+          <t>하락4,000</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>-1.18%</t>
+          <t>-3.92%</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>25,561</t>
+          <t>121,810</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2,581</t>
+          <t>12,133</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>38,209</t>
+          <t>37,149</t>
         </is>
       </c>
     </row>
@@ -4949,32 +4949,32 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>244,000</t>
+          <t>242,000</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>하락2,500</t>
+          <t>하락4,500</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>-1.01%</t>
+          <t>-1.83%</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>6,995</t>
+          <t>31,598</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>1,705</t>
+          <t>7,669</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>37,338</t>
+          <t>37,032</t>
         </is>
       </c>
     </row>
@@ -4989,32 +4989,32 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>83,200</t>
+          <t>81,200</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>상승1,400</t>
+          <t>하락600</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>+1.71%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>9,837</t>
+          <t>42,975</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>806</t>
+          <t>3,514</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>36,867</t>
+          <t>35,981</t>
         </is>
       </c>
     </row>
@@ -5024,37 +5024,37 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>OCI홀딩스</t>
+          <t>롯데케미칼</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>189,100</t>
+          <t>80,500</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>상승6,300</t>
+          <t>상승700</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>+3.45%</t>
+          <t>+0.88%</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>105,614</t>
+          <t>266,406</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20,366</t>
+          <t>21,633</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>35,305</t>
+          <t>34,434</t>
         </is>
       </c>
     </row>
@@ -5064,37 +5064,37 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>현대엘리베이터</t>
+          <t>OCI홀딩스</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>87,400</t>
+          <t>183,300</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>하락600</t>
+          <t>상승500</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>20,678</t>
+          <t>225,854</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>1,811</t>
+          <t>42,629</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>34,167</t>
+          <t>34,223</t>
         </is>
       </c>
     </row>
@@ -5104,37 +5104,37 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>롯데케미칼</t>
+          <t>현대엘리베이터</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>79,600</t>
+          <t>86,700</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>하락200</t>
+          <t>하락1,300</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>-1.48%</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>35,936</t>
+          <t>143,806</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2,868</t>
+          <t>12,542</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>34,049</t>
+          <t>33,893</t>
         </is>
       </c>
     </row>
@@ -5144,37 +5144,37 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>SK바이오사이언스</t>
+          <t>한올바이오파마</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>43,400</t>
+          <t>64,400</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>상승600</t>
+          <t>상승6,500</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>+1.40%</t>
+          <t>+11.23%</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>17,708</t>
+          <t>1,379,671</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>87,809</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>34,041</t>
+          <t>33,643</t>
         </is>
       </c>
     </row>
@@ -5184,37 +5184,37 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>한올바이오파마</t>
+          <t>SK바이오사이언스</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>64,000</t>
+          <t>42,650</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>상승6,100</t>
+          <t>하락150</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>+10.54%</t>
+          <t>-0.35%</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>484,600</t>
+          <t>71,924</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>29,912</t>
+          <t>3,089</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>33,434</t>
+          <t>33,452</t>
         </is>
       </c>
     </row>
@@ -5229,32 +5229,32 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>128,500</t>
+          <t>128,000</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>하락1,500</t>
+          <t>하락2,000</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>-1.15%</t>
+          <t>-1.54%</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>8,989</t>
+          <t>72,585</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>1,162</t>
+          <t>9,327</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>33,451</t>
+          <t>33,321</t>
         </is>
       </c>
     </row>
@@ -5264,37 +5264,37 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>한국가스공사</t>
+          <t>에스원</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>36,100</t>
+          <t>87,500</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>상승100</t>
+          <t>상승600</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>30,607</t>
+          <t>46,831</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>1,102</t>
+          <t>4,098</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>33,325</t>
+          <t>33,249</t>
         </is>
       </c>
     </row>
@@ -5304,37 +5304,37 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>에스원</t>
+          <t>한국가스공사</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>87,000</t>
+          <t>36,000</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>상승100</t>
+          <t>보합0</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>8,126</t>
+          <t>148,566</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>5,334</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>33,059</t>
+          <t>33,233</t>
         </is>
       </c>
     </row>
@@ -5349,32 +5349,32 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>219,000</t>
+          <t>216,500</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>보합0</t>
+          <t>하락2,500</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>6,355</t>
+          <t>30,228</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>1,383</t>
+          <t>6,573</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>32,969</t>
+          <t>32,592</t>
         </is>
       </c>
     </row>
@@ -5384,37 +5384,37 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>한솔케미칼</t>
+          <t>롯데쇼핑</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>288,500</t>
+          <t>114,100</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>상승6,000</t>
+          <t>상승2,800</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>+2.12%</t>
+          <t>+2.52%</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>12,693</t>
+          <t>173,470</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>3,650</t>
+          <t>19,923</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>32,803</t>
+          <t>32,277</t>
         </is>
       </c>
     </row>
@@ -5424,37 +5424,37 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>롯데쇼핑</t>
+          <t>롯데지주</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>115,200</t>
+          <t>30,750</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>상승3,900</t>
+          <t>하락350</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>+3.50%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>33,315</t>
+          <t>270,545</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>3,801</t>
+          <t>8,294</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>32,589</t>
+          <t>32,260</t>
         </is>
       </c>
     </row>
@@ -5464,37 +5464,37 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>신세계</t>
+          <t>한솔케미칼</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>335,000</t>
+          <t>282,500</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>하락2,000</t>
+          <t>보합0</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>-0.59%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>3,654</t>
+          <t>40,522</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>1,219</t>
+          <t>11,558</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>32,311</t>
+          <t>32,121</t>
         </is>
       </c>
     </row>
@@ -5504,37 +5504,37 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>롯데지주</t>
+          <t>신세계</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>30,600</t>
+          <t>332,500</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>하락500</t>
+          <t>하락4,500</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>-1.61%</t>
+          <t>-1.34%</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>54,729</t>
+          <t>25,214</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>1,677</t>
+          <t>8,369</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>32,102</t>
+          <t>32,070</t>
         </is>
       </c>
     </row>
@@ -5549,32 +5549,32 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>223,000</t>
+          <t>219,000</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>상승2,500</t>
+          <t>하락1,500</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>-0.68%</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2,923</t>
+          <t>10,951</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>2,424</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>30,103</t>
+          <t>29,563</t>
         </is>
       </c>
     </row>
@@ -5584,37 +5584,37 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>이수스페셜티케미컬</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>94,500</t>
+          <t>31,150</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>상승3,500</t>
+          <t>하락1,000</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>+3.85%</t>
+          <t>-3.11%</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>137,829</t>
+          <t>446,393</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>12,988</t>
+          <t>13,951</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>28,557</t>
+          <t>27,848</t>
         </is>
       </c>
     </row>
@@ -5624,37 +5624,37 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>에스엘</t>
+          <t>이수스페셜티케미컬</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>59,700</t>
+          <t>91,700</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>하락1,300</t>
+          <t>상승700</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>-2.13%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>19,985</t>
+          <t>318,994</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>1,195</t>
+          <t>29,854</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>27,730</t>
+          <t>27,711</t>
         </is>
       </c>
     </row>
@@ -5664,37 +5664,37 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>HD현대마린엔진</t>
+          <t>에스엘</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>81,900</t>
+          <t>59,200</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>상승4,400</t>
+          <t>하락1,800</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>+5.68%</t>
+          <t>-2.95%</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>316,824</t>
+          <t>126,309</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>26,042</t>
+          <t>7,476</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>27,782</t>
+          <t>27,498</t>
         </is>
       </c>
     </row>
@@ -5704,37 +5704,37 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>iM금융지주</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>31,000</t>
+          <t>16,980</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>하락1,150</t>
+          <t>보합0</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>-3.58%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>140,215</t>
+          <t>486,688</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>4,391</t>
+          <t>8,340</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>27,714</t>
+          <t>27,274</t>
         </is>
       </c>
     </row>
@@ -5749,32 +5749,32 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>61,200</t>
+          <t>60,600</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>하락1,600</t>
+          <t>하락2,200</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>-2.55%</t>
+          <t>-3.50%</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>53,962</t>
+          <t>182,018</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>3,324</t>
+          <t>11,128</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>27,540</t>
+          <t>27,270</t>
         </is>
       </c>
     </row>
@@ -5784,37 +5784,37 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>iM금융지주</t>
+          <t>동서</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>17,050</t>
+          <t>27,250</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>상승70</t>
+          <t>상승50</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>+0.18%</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>46,421</t>
+          <t>68,353</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>1,854</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>27,386</t>
+          <t>27,168</t>
         </is>
       </c>
     </row>
@@ -5824,37 +5824,37 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>동서</t>
+          <t>이마트</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>27,100</t>
+          <t>97,800</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>하락100</t>
+          <t>하락700</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>-0.37%</t>
+          <t>-0.71%</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>14,803</t>
+          <t>142,619</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>13,927</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>27,019</t>
+          <t>26,989</t>
         </is>
       </c>
     </row>
@@ -5864,37 +5864,37 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>이마트</t>
+          <t>HD현대마린엔진</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>97,900</t>
+          <t>78,800</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>하락600</t>
+          <t>상승1,300</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>-0.61%</t>
+          <t>+1.68%</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>42,663</t>
+          <t>509,127</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>4,162</t>
+          <t>41,416</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>27,016</t>
+          <t>26,730</t>
         </is>
       </c>
     </row>
@@ -5904,37 +5904,37 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>풍산</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>96,200</t>
+          <t>4,980</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>하락2,000</t>
+          <t>하락100</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>-2.04%</t>
+          <t>-1.97%</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>57,134</t>
+          <t>3,051,959</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>5,520</t>
+          <t>15,210</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>26,959</t>
+          <t>26,622</t>
         </is>
       </c>
     </row>
@@ -5944,37 +5944,37 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>풍산</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>5,010</t>
+          <t>93,500</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>하락70</t>
+          <t>하락4,700</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>-1.38%</t>
+          <t>-4.79%</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>442,335</t>
+          <t>214,655</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2,231</t>
+          <t>20,428</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>26,782</t>
+          <t>26,203</t>
         </is>
       </c>
     </row>
@@ -5989,32 +5989,32 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>62,500</t>
+          <t>62,100</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>하락800</t>
+          <t>하락1,200</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>-1.26%</t>
+          <t>-1.90%</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>209,108</t>
+          <t>585,732</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>13,228</t>
+          <t>37,036</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>26,357</t>
+          <t>26,188</t>
         </is>
       </c>
     </row>
@@ -6029,32 +6029,32 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>38,550</t>
+          <t>37,950</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>상승850</t>
+          <t>상승250</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>+2.25%</t>
+          <t>+0.66%</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>27,208</t>
+          <t>111,711</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>1,038</t>
+          <t>4,242</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>26,365</t>
+          <t>25,955</t>
         </is>
       </c>
     </row>
@@ -6064,37 +6064,37 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>한국앤컴퍼니</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>66,800</t>
+          <t>27,100</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>하락2,500</t>
+          <t>하락500</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>-3.61%</t>
+          <t>-1.81%</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>671,166</t>
+          <t>86,413</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>45,178</t>
+          <t>2,324</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>25,847</t>
+          <t>25,727</t>
         </is>
       </c>
     </row>
@@ -6104,37 +6104,37 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>한국앤컴퍼니</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>26,750</t>
+          <t>66,400</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>하락850</t>
+          <t>하락2,900</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>-3.08%</t>
+          <t>-4.18%</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>18,483</t>
+          <t>1,574,485</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>497</t>
+          <t>104,826</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>25,395</t>
+          <t>25,693</t>
         </is>
       </c>
     </row>
@@ -6149,32 +6149,32 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>70,500</t>
+          <t>70,200</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>하락2,000</t>
+          <t>하락2,300</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>-2.76%</t>
+          <t>-3.17%</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>92,696</t>
+          <t>226,183</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>6,581</t>
+          <t>15,984</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>25,283</t>
+          <t>25,175</t>
         </is>
       </c>
     </row>
@@ -6189,32 +6189,32 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>110,500</t>
+          <t>108,000</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>하락1,600</t>
+          <t>하락4,100</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>-1.43%</t>
+          <t>-3.66%</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>5,159</t>
+          <t>68,267</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>7,400</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>25,208</t>
+          <t>24,637</t>
         </is>
       </c>
     </row>
@@ -6229,32 +6229,32 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>51,800</t>
+          <t>51,500</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>하락600</t>
+          <t>하락900</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>-1.15%</t>
+          <t>-1.72%</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>43,187</t>
+          <t>173,130</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2,242</t>
+          <t>8,925</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>24,324</t>
+          <t>24,183</t>
         </is>
       </c>
     </row>
@@ -6264,37 +6264,37 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>F&amp;F</t>
+          <t>DN오토모티브</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>61,400</t>
+          <t>41,250</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>하락1,400</t>
+          <t>상승2,050</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>-2.23%</t>
+          <t>+5.23%</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>15,559</t>
+          <t>413,850</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>16,741</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>23,521</t>
+          <t>24,136</t>
         </is>
       </c>
     </row>
@@ -6304,37 +6304,37 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>제일기획</t>
+          <t>F&amp;F</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>20,050</t>
+          <t>62,300</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>보합0</t>
+          <t>하락500</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-0.80%</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>58,985</t>
+          <t>64,343</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>1,183</t>
+          <t>3,981</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>23,066</t>
+          <t>23,865</t>
         </is>
       </c>
     </row>
@@ -6344,37 +6344,37 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>DN오토모티브</t>
+          <t>제일기획</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>39,200</t>
+          <t>19,830</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>보합0</t>
+          <t>하락220</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-1.10%</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>43,880</t>
+          <t>533,111</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>1,722</t>
+          <t>10,597</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>22,936</t>
+          <t>22,813</t>
         </is>
       </c>
     </row>
@@ -6389,32 +6389,32 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>375,000</t>
+          <t>373,500</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>하락3,500</t>
+          <t>하락5,000</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>-0.92%</t>
+          <t>-1.32%</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>4,070</t>
+          <t>18,997</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>1,525</t>
+          <t>7,113</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>22,810</t>
+          <t>22,719</t>
         </is>
       </c>
     </row>
@@ -6429,32 +6429,32 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>26,600</t>
+          <t>26,250</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>하락800</t>
+          <t>하락1,150</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>-2.92%</t>
+          <t>-4.20%</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>665,999</t>
+          <t>1,740,461</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>17,704</t>
+          <t>46,047</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>22,765</t>
+          <t>22,465</t>
         </is>
       </c>
     </row>
@@ -6464,37 +6464,37 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>현대위아</t>
+          <t>한국카본</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>82,300</t>
+          <t>42,800</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>하락300</t>
+          <t>상승950</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>-0.36%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>17,074</t>
+          <t>1,055,624</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>1,402</t>
+          <t>45,798</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>22,382</t>
+          <t>22,217</t>
         </is>
       </c>
     </row>
@@ -6504,37 +6504,37 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>한국카본</t>
+          <t>코오롱인더</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>43,150</t>
+          <t>80,500</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>상승1,300</t>
+          <t>상승1,700</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>+3.11%</t>
+          <t>+2.16%</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>603,358</t>
+          <t>637,640</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>26,442</t>
+          <t>52,302</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>22,398</t>
+          <t>22,153</t>
         </is>
       </c>
     </row>
@@ -6544,37 +6544,37 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>코오롱인더</t>
+          <t>현대위아</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>81,300</t>
+          <t>81,000</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>상승2,500</t>
+          <t>하락1,600</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>+3.17%</t>
+          <t>-1.94%</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>130,754</t>
+          <t>98,141</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>10,541</t>
+          <t>7,995</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>22,373</t>
+          <t>22,028</t>
         </is>
       </c>
     </row>
@@ -6584,37 +6584,37 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>BGF리테일</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>193,400</t>
+          <t>125,100</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>하락2,900</t>
+          <t>상승2,200</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>-1.48%</t>
+          <t>+1.79%</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>8,613</t>
+          <t>33,673</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>1,680</t>
+          <t>4,176</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>21,950</t>
+          <t>21,622</t>
         </is>
       </c>
     </row>
@@ -6624,37 +6624,37 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>아모레퍼시픽홀딩스</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>28,050</t>
+          <t>188,800</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>하락300</t>
+          <t>하락7,500</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>-1.06%</t>
+          <t>-3.82%</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>22,710</t>
+          <t>50,332</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>9,623</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>21,447</t>
+          <t>21,428</t>
         </is>
       </c>
     </row>
@@ -6664,37 +6664,37 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>미스토홀딩스</t>
+          <t>아모레퍼시픽홀딩스</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>40,300</t>
+          <t>27,850</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>하락1,900</t>
+          <t>하락500</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>-4.50%</t>
+          <t>-1.76%</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>35,989</t>
+          <t>102,100</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>1,453</t>
+          <t>2,871</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>21,396</t>
+          <t>21,294</t>
         </is>
       </c>
     </row>
@@ -6704,37 +6704,37 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>BGF리테일</t>
+          <t>미스토홀딩스</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>123,100</t>
+          <t>40,100</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>상승200</t>
+          <t>하락2,100</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-4.98%</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>6,473</t>
+          <t>160,204</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>794</t>
+          <t>6,428</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>21,276</t>
+          <t>21,290</t>
         </is>
       </c>
     </row>
@@ -6749,32 +6749,32 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>84,300</t>
+          <t>84,500</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>하락2,500</t>
+          <t>하락2,300</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>-2.88%</t>
+          <t>-2.65%</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>14,781</t>
+          <t>77,192</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>1,256</t>
+          <t>6,513</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>19,076</t>
+          <t>19,121</t>
         </is>
       </c>
     </row>
@@ -6789,32 +6789,32 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>163,800</t>
+          <t>161,400</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>상승4,400</t>
+          <t>상승2,000</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>+2.76%</t>
+          <t>+1.25%</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>8,617</t>
+          <t>27,911</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>1,399</t>
+          <t>4,526</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>18,979</t>
+          <t>18,701</t>
         </is>
       </c>
     </row>
@@ -6829,32 +6829,32 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>78,800</t>
+          <t>77,400</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>하락800</t>
+          <t>하락2,200</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>-1.01%</t>
+          <t>-2.76%</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>39,658</t>
+          <t>162,266</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>3,112</t>
+          <t>12,620</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>18,601</t>
+          <t>18,270</t>
         </is>
       </c>
     </row>
@@ -6864,37 +6864,37 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>SK아이이테크놀로지</t>
+          <t>동원산업</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>21,700</t>
+          <t>39,950</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>하락400</t>
+          <t>하락50</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>-1.81%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>29,861</t>
+          <t>33,344</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>1,329</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>17,748</t>
+          <t>17,637</t>
         </is>
       </c>
     </row>
@@ -6904,37 +6904,37 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>동원산업</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>39,950</t>
+          <t>6,100</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>하락50</t>
+          <t>하락120</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>7,995</t>
+          <t>310,527</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>1,893</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>17,637</t>
+          <t>17,523</t>
         </is>
       </c>
     </row>
@@ -6944,37 +6944,37 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>녹십자</t>
+          <t>GS리테일</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>150,500</t>
+          <t>20,950</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>상승1,500</t>
+          <t>상승350</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>+1.01%</t>
+          <t>+1.70%</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>8,792</t>
+          <t>160,037</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>1,320</t>
+          <t>3,358</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>17,588</t>
+          <t>17,516</t>
         </is>
       </c>
     </row>
@@ -6984,37 +6984,37 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>녹십자</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>6,100</t>
+          <t>148,300</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>하락120</t>
+          <t>하락700</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>-1.93%</t>
+          <t>-0.47%</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>81,222</t>
+          <t>33,879</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>5,063</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>17,523</t>
+          <t>17,331</t>
         </is>
       </c>
     </row>
@@ -7024,37 +7024,37 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>GS리테일</t>
+          <t>SK아이이테크놀로지</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>20,750</t>
+          <t>21,050</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>상승150</t>
+          <t>하락1,050</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>+0.73%</t>
+          <t>-4.75%</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>21,906</t>
+          <t>162,509</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>454</t>
+          <t>3,467</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>17,349</t>
+          <t>17,216</t>
         </is>
       </c>
     </row>
@@ -7069,32 +7069,32 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>393,000</t>
+          <t>389,500</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>상승8,000</t>
+          <t>상승4,500</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>+2.08%</t>
+          <t>+1.17%</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>10,444</t>
+          <t>35,949</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>4,123</t>
+          <t>14,173</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>17,008</t>
+          <t>16,856</t>
         </is>
       </c>
     </row>
@@ -7109,32 +7109,32 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>42,150</t>
+          <t>41,950</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>하락550</t>
+          <t>하락750</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>-1.76%</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>43,806</t>
+          <t>162,594</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>1,845</t>
+          <t>6,816</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>16,543</t>
+          <t>16,465</t>
         </is>
       </c>
     </row>
@@ -7144,37 +7144,37 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>파라다이스</t>
+          <t>오리온홀딩스</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>17,360</t>
+          <t>25,450</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>상승390</t>
+          <t>상승600</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>+2.30%</t>
+          <t>+2.41%</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>182,892</t>
+          <t>321,854</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>3,159</t>
+          <t>8,142</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>16,080</t>
+          <t>15,943</t>
         </is>
       </c>
     </row>
@@ -7184,37 +7184,37 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>오리온홀딩스</t>
+          <t>파라다이스</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>24,900</t>
+          <t>16,990</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>상승50</t>
+          <t>상승20</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>24,749</t>
+          <t>547,299</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>9,433</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>15,599</t>
+          <t>15,738</t>
         </is>
       </c>
     </row>
@@ -7229,32 +7229,32 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>365,500</t>
+          <t>362,500</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>하락5,000</t>
+          <t>하락8,000</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>-1.35%</t>
+          <t>-2.16%</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>1,118</t>
+          <t>4,849</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>1,765</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>14,649</t>
+          <t>14,528</t>
         </is>
       </c>
     </row>
@@ -7269,32 +7269,32 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>25,200</t>
+          <t>24,450</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>상승900</t>
+          <t>상승150</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>+3.70%</t>
+          <t>+0.62%</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>33,529</t>
+          <t>100,049</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>836</t>
+          <t>2,484</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>14,652</t>
+          <t>14,216</t>
         </is>
       </c>
     </row>
@@ -7324,12 +7324,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>15,240</t>
+          <t>78,156</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>4,043</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -7349,32 +7349,32 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>1,196,000</t>
+          <t>1,179,000</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>하락15,000</t>
+          <t>하락32,000</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>-1.24%</t>
+          <t>-2.64%</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>1,964</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>2,332</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>13,316</t>
+          <t>13,127</t>
         </is>
       </c>
     </row>
@@ -7384,37 +7384,37 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>DL</t>
+          <t>종근당</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>60,500</t>
+          <t>91,700</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>상승2,300</t>
+          <t>상승1,900</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>+3.95%</t>
+          <t>+2.12%</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>57,906</t>
+          <t>49,239</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>3,490</t>
+          <t>4,560</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>12,678</t>
+          <t>12,657</t>
         </is>
       </c>
     </row>
@@ -7424,37 +7424,37 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>종근당</t>
+          <t>DL</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>91,700</t>
+          <t>59,400</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>상승1,900</t>
+          <t>상승1,200</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>+2.12%</t>
+          <t>+2.06%</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>11,800</t>
+          <t>137,636</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>1,080</t>
+          <t>8,243</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>12,657</t>
+          <t>12,448</t>
         </is>
       </c>
     </row>
@@ -7469,32 +7469,32 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>16,770</t>
+          <t>16,590</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>하락240</t>
+          <t>하락420</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>-1.41%</t>
+          <t>-2.47%</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>19,687</t>
+          <t>99,974</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>1,666</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>12,334</t>
+          <t>12,201</t>
         </is>
       </c>
     </row>
@@ -7509,32 +7509,32 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>16,560</t>
+          <t>16,540</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>하락100</t>
+          <t>하락120</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>-0.60%</t>
+          <t>-0.72%</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>46,313</t>
+          <t>118,977</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>1,969</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>11,614</t>
+          <t>11,600</t>
         </is>
       </c>
     </row>
@@ -7549,32 +7549,32 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>61,700</t>
+          <t>60,900</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>하락1,100</t>
+          <t>하락1,900</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>-1.75%</t>
+          <t>-3.03%</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>12,555</t>
+          <t>45,807</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>2,819</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>11,154</t>
+          <t>11,009</t>
         </is>
       </c>
     </row>
@@ -7589,32 +7589,32 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>118,600</t>
+          <t>117,000</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>하락1,300</t>
+          <t>하락2,900</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>-1.08%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>2,900</t>
+          <t>20,264</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>2,385</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>11,005</t>
+          <t>10,856</t>
         </is>
       </c>
     </row>
@@ -7644,12 +7644,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>3,714</t>
+          <t>30,425</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>1,525</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -7684,12 +7684,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>3,381</t>
+          <t>21,579</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>2,460</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -7709,32 +7709,32 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>91,300</t>
+          <t>90,200</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>상승100</t>
+          <t>하락1,000</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-1.10%</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>11,058</t>
+          <t>54,770</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>1,009</t>
+          <t>4,960</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>10,571</t>
+          <t>10,444</t>
         </is>
       </c>
     </row>
@@ -7749,32 +7749,32 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>43,400</t>
+          <t>42,800</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>하락200</t>
+          <t>하락800</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>-0.46%</t>
+          <t>-1.83%</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>3,792</t>
+          <t>16,072</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>691</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>10,214</t>
+          <t>10,073</t>
         </is>
       </c>
     </row>
@@ -7789,32 +7789,32 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>222,500</t>
+          <t>221,500</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>하락2,000</t>
+          <t>하락3,000</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>-0.89%</t>
+          <t>-1.34%</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>1,924</t>
+          <t>10,577</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>2,362</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>9,968</t>
+          <t>9,923</t>
         </is>
       </c>
     </row>
@@ -7829,32 +7829,32 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>8,070</t>
+          <t>7,940</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>상승140</t>
+          <t>상승10</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>+1.77%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>25,684</t>
+          <t>87,978</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>702</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>9,825</t>
+          <t>9,667</t>
         </is>
       </c>
     </row>
@@ -7869,32 +7869,32 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>55,800</t>
+          <t>54,300</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>하락400</t>
+          <t>하락1,900</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>-0.71%</t>
+          <t>-3.38%</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>8,328</t>
+          <t>45,828</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>2,525</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>9,653</t>
+          <t>9,393</t>
         </is>
       </c>
     </row>
@@ -7909,32 +7909,32 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>134,100</t>
+          <t>137,800</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>하락1,600</t>
+          <t>상승2,100</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>-1.18%</t>
+          <t>+1.55%</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>6,276</t>
+          <t>69,677</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>9,635</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>8,716</t>
+          <t>8,957</t>
         </is>
       </c>
     </row>
@@ -7949,32 +7949,32 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>60,800</t>
+          <t>60,600</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>하락600</t>
+          <t>하락800</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>-0.98%</t>
+          <t>-1.30%</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>4,091</t>
+          <t>23,220</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>1,404</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>8,427</t>
+          <t>8,399</t>
         </is>
       </c>
     </row>
@@ -7984,37 +7984,37 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>세아제강지주</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>7,480</t>
+          <t>192,000</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>상승140</t>
+          <t>상승5,200</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>+1.91%</t>
+          <t>+2.78%</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>120,912</t>
+          <t>50,711</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>893</t>
+          <t>9,598</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>8,023</t>
+          <t>7,952</t>
         </is>
       </c>
     </row>
@@ -8024,37 +8024,37 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>세아제강지주</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>186,000</t>
+          <t>7,210</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>하락800</t>
+          <t>하락130</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>-1.77%</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>14,469</t>
+          <t>365,214</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2,723</t>
+          <t>2,678</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>7,703</t>
+          <t>7,733</t>
         </is>
       </c>
     </row>
@@ -8069,32 +8069,32 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>26,400</t>
+          <t>26,450</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>하락250</t>
+          <t>하락200</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>-0.94%</t>
+          <t>-0.75%</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>12,231</t>
+          <t>31,671</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>834</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>7,654</t>
+          <t>7,668</t>
         </is>
       </c>
     </row>
@@ -8109,32 +8109,32 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>18,480</t>
+          <t>18,570</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>하락180</t>
+          <t>하락90</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>-0.96%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>13,852</t>
+          <t>58,043</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>1,075</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>7,554</t>
+          <t>7,591</t>
         </is>
       </c>
     </row>
@@ -8149,32 +8149,32 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>11,980</t>
+          <t>11,790</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>하락20</t>
+          <t>하락210</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-1.75%</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>43,604</t>
+          <t>238,999</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>2,839</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>7,410</t>
+          <t>7,293</t>
         </is>
       </c>
     </row>
@@ -8189,32 +8189,32 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>20,925</t>
+          <t>20,600</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>하락125</t>
+          <t>하락450</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>-0.59%</t>
+          <t>-2.14%</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>34,070</t>
+          <t>127,838</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>2,656</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>7,250</t>
+          <t>7,137</t>
         </is>
       </c>
     </row>
@@ -8229,32 +8229,32 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>14,150</t>
+          <t>14,100</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>상승20</t>
+          <t>하락30</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>25,054</t>
+          <t>100,686</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>1,426</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>6,654</t>
+          <t>6,631</t>
         </is>
       </c>
     </row>
@@ -8269,32 +8269,32 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>136,100</t>
+          <t>137,500</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>하락500</t>
+          <t>상승900</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>-0.37%</t>
+          <t>+0.66%</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>1,430</t>
+          <t>2,677</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>365</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>6,465</t>
+          <t>6,531</t>
         </is>
       </c>
     </row>
@@ -8309,32 +8309,32 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>126,200</t>
+          <t>126,800</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>하락2,300</t>
+          <t>하락1,700</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>-1.79%</t>
+          <t>-1.32%</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>1,935</t>
+          <t>2,876</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>361</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>6,310</t>
+          <t>6,340</t>
         </is>
       </c>
     </row>
@@ -8349,32 +8349,32 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>24,000</t>
+          <t>23,850</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>상승300</t>
+          <t>상승150</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>+1.27%</t>
+          <t>+0.63%</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>27,005</t>
+          <t>91,050</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>2,180</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>5,952</t>
+          <t>5,915</t>
         </is>
       </c>
     </row>
@@ -8389,32 +8389,32 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>15,320</t>
+          <t>15,130</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>상승130</t>
+          <t>하락60</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>+0.86%</t>
+          <t>-0.39%</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>64,306</t>
+          <t>186,437</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>2,831</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>5,884</t>
+          <t>5,811</t>
         </is>
       </c>
     </row>
@@ -8429,32 +8429,32 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>273,500</t>
+          <t>278,500</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>하락5,000</t>
+          <t>보합0</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>-1.80%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>2,143</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>589</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>5,669</t>
+          <t>5,772</t>
         </is>
       </c>
     </row>
